--- a/data/reporte_20260429.xlsx
+++ b/data/reporte_20260429.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\taully_demand_forecast\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\taully_demand_forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F44DD9-1F8B-4057-A093-71C0BDD3D4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE91242-D9BE-4526-A13F-A1C496A36676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{77C3973B-AC8A-4C74-A1D9-4DA080B93A65}"/>
+    <workbookView xWindow="1890" yWindow="3255" windowWidth="20460" windowHeight="10770" xr2:uid="{77C3973B-AC8A-4C74-A1D9-4DA080B93A65}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -488,10 +488,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2188CDE1-77FF-425F-8498-E1BD15503837}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -638,6 +638,12 @@
         <v>23</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
